--- a/Team-Data/2007-08/1-10-2007-08.xlsx
+++ b/Team-Data/2007-08/1-10-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -787,7 +854,7 @@
         <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="n">
         <v>23</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>12.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -954,7 +1021,7 @@
         <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP3" t="n">
         <v>7</v>
@@ -972,13 +1039,13 @@
         <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>-4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
@@ -1115,7 +1182,7 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
@@ -1133,7 +1200,7 @@
         <v>18</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-3.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>1</v>
@@ -1345,7 +1412,7 @@
         <v>16</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
@@ -1482,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -1649,22 +1716,22 @@
         <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>4</v>
       </c>
       <c r="AF7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH7" t="n">
         <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
         <v>25</v>
@@ -1691,10 +1758,10 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1843,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1885,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.75</v>
+        <v>0.743</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
@@ -1953,7 +2020,7 @@
         <v>37.1</v>
       </c>
       <c r="J9" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0.466</v>
@@ -1962,37 +2029,37 @@
         <v>5.9</v>
       </c>
       <c r="M9" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P9" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q9" t="n">
         <v>0.764</v>
       </c>
       <c r="R9" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S9" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T9" t="n">
         <v>40.7</v>
       </c>
       <c r="U9" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V9" t="n">
         <v>11.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
         <v>5.2</v>
@@ -2004,16 +2071,16 @@
         <v>20.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,10 +2095,10 @@
         <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
         <v>6</v>
@@ -2049,19 +2116,19 @@
         <v>12</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
         <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU9" t="n">
         <v>6</v>
@@ -2070,10 +2137,10 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2225,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>1.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
         <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>20</v>
@@ -2422,7 +2489,7 @@
         <v>7</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2653,7 @@
         <v>4</v>
       </c>
       <c r="AM12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
         <v>11</v>
@@ -2601,7 +2668,7 @@
         <v>19</v>
       </c>
       <c r="AR12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2826,7 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>6.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2953,13 +3020,13 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
@@ -2983,7 +3050,7 @@
         <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -3027,85 +3094,85 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.286</v>
+        <v>0.294</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J15" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M15" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R15" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="S15" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>41.3</v>
+        <v>41.6</v>
       </c>
       <c r="U15" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="W15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X15" t="n">
         <v>5.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.5</v>
+        <v>100.1</v>
       </c>
       <c r="AC15" t="n">
         <v>-4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3117,16 +3184,16 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL15" t="n">
         <v>6</v>
@@ -3135,13 +3202,13 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
         <v>16</v>
@@ -3150,16 +3217,16 @@
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>21</v>
       </c>
       <c r="AV15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW15" t="n">
         <v>30</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>29</v>
@@ -3302,13 +3369,13 @@
         <v>9</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ16" t="n">
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3332,7 +3399,7 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
@@ -3487,7 +3554,7 @@
         <v>18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
         <v>17</v>
@@ -3511,13 +3578,13 @@
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU17" t="n">
         <v>14</v>
@@ -3526,7 +3593,7 @@
         <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="n">
         <v>19</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-4</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
@@ -3869,7 +3936,7 @@
         <v>9</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4054,7 +4121,7 @@
         <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
         <v>15</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-7.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>27</v>
       </c>
       <c r="AF21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG21" t="n">
         <v>27</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
@@ -4221,7 +4288,7 @@
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>18</v>
@@ -4230,7 +4297,7 @@
         <v>22</v>
       </c>
       <c r="AO21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP21" t="n">
         <v>12</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4464,7 @@
         <v>13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
         <v>7</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>21</v>
@@ -4618,7 +4685,7 @@
         <v>23</v>
       </c>
       <c r="AW23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -4665,70 +4732,70 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" t="n">
         <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>0.694</v>
+        <v>0.714</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="J24" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.488</v>
+        <v>0.492</v>
       </c>
       <c r="L24" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.381</v>
+        <v>0.383</v>
       </c>
       <c r="O24" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P24" t="n">
         <v>22.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="R24" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T24" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U24" t="n">
-        <v>27.5</v>
+        <v>27.8</v>
       </c>
       <c r="V24" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W24" t="n">
         <v>7.2</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z24" t="n">
         <v>19.4</v>
@@ -4737,13 +4804,13 @@
         <v>20.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>110</v>
+        <v>110.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4755,7 +4822,7 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4764,13 +4831,13 @@
         <v>4</v>
       </c>
       <c r="AK24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="n">
         <v>3</v>
       </c>
       <c r="AM24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN24" t="n">
         <v>4</v>
@@ -4791,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4964,10 +5031,10 @@
         <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -5029,61 +5096,61 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26" t="n">
         <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.412</v>
+        <v>0.394</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>35.5</v>
+        <v>35.3</v>
       </c>
       <c r="J26" t="n">
-        <v>78.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M26" t="n">
         <v>16.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O26" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="P26" t="n">
         <v>27.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.792</v>
+        <v>0.788</v>
       </c>
       <c r="R26" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="S26" t="n">
         <v>29.2</v>
       </c>
       <c r="T26" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="U26" t="n">
         <v>17.9</v>
       </c>
       <c r="V26" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="W26" t="n">
         <v>8</v>
@@ -5092,25 +5159,25 @@
         <v>3.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA26" t="n">
         <v>23.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF26" t="n">
         <v>19</v>
@@ -5119,10 +5186,10 @@
         <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
@@ -5140,16 +5207,16 @@
         <v>17</v>
       </c>
       <c r="AO26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP26" t="n">
         <v>8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AR26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
         <v>25</v>
@@ -5164,13 +5231,13 @@
         <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
         <v>28</v>
       </c>
       <c r="AY26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ26" t="n">
         <v>24</v>
@@ -5179,7 +5246,7 @@
         <v>5</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -5211,37 +5278,37 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" t="n">
         <v>23</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>0.676</v>
+        <v>0.697</v>
       </c>
       <c r="H27" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>79.3</v>
+        <v>79.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M27" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="N27" t="n">
-        <v>0.385</v>
+        <v>0.387</v>
       </c>
       <c r="O27" t="n">
         <v>17.2</v>
@@ -5253,16 +5320,16 @@
         <v>0.758</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S27" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T27" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U27" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="V27" t="n">
         <v>12.5</v>
@@ -5271,7 +5338,7 @@
         <v>6.2</v>
       </c>
       <c r="X27" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y27" t="n">
         <v>4.8</v>
@@ -5283,13 +5350,13 @@
         <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
         <v>5</v>
@@ -5298,19 +5365,19 @@
         <v>3</v>
       </c>
       <c r="AG27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH27" t="n">
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ27" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL27" t="n">
         <v>5</v>
@@ -5331,16 +5398,16 @@
         <v>15</v>
       </c>
       <c r="AR27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AS27" t="n">
         <v>12</v>
       </c>
       <c r="AT27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV27" t="n">
         <v>3</v>
@@ -5361,7 +5428,7 @@
         <v>22</v>
       </c>
       <c r="BB27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5483,7 +5550,7 @@
         <v>28</v>
       </c>
       <c r="AH28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI28" t="n">
         <v>7</v>
@@ -5501,7 +5568,7 @@
         <v>27</v>
       </c>
       <c r="AN28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO28" t="n">
         <v>19</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5695,16 +5762,16 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS29" t="n">
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" t="n">
         <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>0.541</v>
+        <v>0.528</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,7 +5842,7 @@
         <v>39.6</v>
       </c>
       <c r="J30" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0.489</v>
@@ -5784,61 +5851,61 @@
         <v>3.9</v>
       </c>
       <c r="M30" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="N30" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O30" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="P30" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R30" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="S30" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T30" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="U30" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="V30" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W30" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>104.8</v>
+        <v>104.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF30" t="n">
         <v>14</v>
@@ -5856,7 +5923,7 @@
         <v>14</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL30" t="n">
         <v>29</v>
@@ -5865,25 +5932,25 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5892,7 +5959,7 @@
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>17</v>
@@ -6056,7 +6123,7 @@
         <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-10-2007-08</t>
+          <t>2008-01-10</t>
         </is>
       </c>
     </row>
